--- a/output/roomself_excel/11296.xlsx
+++ b/output/roomself_excel/11296.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>662539</v>
+        <v>202070</v>
       </c>
       <c r="D2" t="n">
-        <v>10724</v>
+        <v>3624</v>
       </c>
       <c r="E2" t="n">
-        <v>1252</v>
+        <v>440</v>
       </c>
       <c r="F2" t="n">
-        <v>1080</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>230992</v>
+        <v>300564</v>
       </c>
       <c r="D3" t="n">
-        <v>3848</v>
+        <v>4420</v>
       </c>
       <c r="E3" t="n">
-        <v>496</v>
+        <v>652</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>192397</v>
+        <v>112690</v>
       </c>
       <c r="D4" t="n">
-        <v>3512</v>
+        <v>2708</v>
       </c>
       <c r="E4" t="n">
-        <v>519</v>
+        <v>295</v>
       </c>
       <c r="F4" t="n">
-        <v>452</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34625</v>
+        <v>64291</v>
       </c>
       <c r="D5" t="n">
-        <v>1608</v>
+        <v>2032</v>
       </c>
       <c r="E5" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>233402</v>
+        <v>159905</v>
       </c>
       <c r="D6" t="n">
-        <v>3972</v>
+        <v>4312</v>
       </c>
       <c r="E6" t="n">
-        <v>642</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,17 +576,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>112690</v>
+        <v>34625</v>
       </c>
       <c r="D7" t="n">
-        <v>2708</v>
+        <v>1608</v>
       </c>
       <c r="E7" t="n">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="F7" t="n">
         <v>31</v>
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>64291</v>
+        <v>192397</v>
       </c>
       <c r="D8" t="n">
-        <v>2032</v>
+        <v>3512</v>
       </c>
       <c r="E8" t="n">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F8" t="n">
-        <v>270</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -624,15 +624,59 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>230992</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3848</v>
+      </c>
+      <c r="E9" t="n">
+        <v>496</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>233402</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3972</v>
+      </c>
+      <c r="E10" t="n">
+        <v>642</v>
+      </c>
+      <c r="F10" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>40929</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>1744</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>269</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>229</v>
       </c>
     </row>

--- a/output/roomself_excel/11296.xlsx
+++ b/output/roomself_excel/11296.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3624</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>440</v>
       </c>
-      <c r="F2" t="n">
-        <v>31</v>
-      </c>
+      <c r="G2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>4420</v>
       </c>
-      <c r="E3" t="n">
-        <v>652</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>515</v>
+        <v>484</v>
+      </c>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>621</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +563,20 @@
       <c r="D4" t="n">
         <v>2708</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>295</v>
       </c>
-      <c r="F4" t="n">
-        <v>31</v>
-      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>2032</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>269</v>
       </c>
-      <c r="F5" t="n">
-        <v>31</v>
-      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +623,12 @@
       <c r="D6" t="n">
         <v>4312</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +645,20 @@
       <c r="D7" t="n">
         <v>1608</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>258</v>
       </c>
-      <c r="F7" t="n">
-        <v>31</v>
-      </c>
+      <c r="G7" t="n">
+        <v>31</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +675,27 @@
       <c r="D8" t="n">
         <v>3512</v>
       </c>
-      <c r="E8" t="n">
-        <v>519</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>452</v>
+        <v>842</v>
+      </c>
+      <c r="G8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>457</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +713,20 @@
       <c r="D9" t="n">
         <v>3848</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>496</v>
       </c>
-      <c r="F9" t="n">
-        <v>31</v>
-      </c>
+      <c r="G9" t="n">
+        <v>31</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +743,27 @@
       <c r="D10" t="n">
         <v>3972</v>
       </c>
-      <c r="E10" t="n">
-        <v>642</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>413</v>
+        <v>382</v>
+      </c>
+      <c r="G10" t="n">
+        <v>31</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>611</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -673,11 +781,27 @@
       <c r="D11" t="n">
         <v>1744</v>
       </c>
-      <c r="E11" t="n">
-        <v>269</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>229</v>
+        <v>238</v>
+      </c>
+      <c r="G11" t="n">
+        <v>31</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>198</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
